--- a/assets/data/search_methods/ukllc_catalogue/File_2_Documentation_Master.xlsx
+++ b/assets/data/search_methods/ukllc_catalogue/File_2_Documentation_Master.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\LHA_UKLLC\Deposits\Data_and_Metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UCL\Github\OWL\assets\data\search_methods\ukllc_catalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7179A766-1769-4CFC-8B71-399CB733CE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D494034-B940-4926-A6DB-13F4C12BB4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{BF5C6858-8849-464B-BFFF-EA4DD55D1A19}"/>
+    <workbookView xWindow="-37620" yWindow="720" windowWidth="26130" windowHeight="15480" xr2:uid="{BF5C6858-8849-464B-BFFF-EA4DD55D1A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -439,9 +450,6 @@
     <t xml:space="preserve">APOE for SNPs rs7413 and rs429358. The SNPs were measured from blood samples taken at the 1999 data collection. If there was missing data from 1999, the measures were taken from the Insight 46 wave 1 sub-study (2018-2021).  </t>
   </si>
   <si>
-    <t>NSHD46_APOE_v0001_20260217.csv</t>
-  </si>
-  <si>
     <t>NSHD46_APOE_v0001_values_20260217.csv</t>
   </si>
   <si>
@@ -490,9 +498,6 @@
     <t>agecl23x</t>
   </si>
   <si>
-    <t>NSHD46_CAT-2011_Blood_Biochemistry_v0001_20260812.csv</t>
-  </si>
-  <si>
     <t>NSHD46_CAT-2011_Blood_Biochemistry_v0001_description_20260812.csv</t>
   </si>
   <si>
@@ -535,9 +540,6 @@
     <t>height, weight, body mass index (bmi), physical measures</t>
   </si>
   <si>
-    <t>NSHD46_CAT-1103_BP_v0001_20260812.csv</t>
-  </si>
-  <si>
     <t>NSHD46_CAT-1103_BP_v0001_description_20260812.csv</t>
   </si>
   <si>
@@ -848,6 +850,15 @@
   </si>
   <si>
     <t>housing, household, accomadation, children, grandchildren, vehicles, pets</t>
+  </si>
+  <si>
+    <t>NSHD46_APOE_v0001_2026022.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-2011_Blood_Biochemistry_v0001_20260814.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-1103_BP_v0001_20260814.csv</t>
   </si>
 </sst>
 </file>
@@ -1159,7 +1170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1233,6 +1244,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1250,16 +1264,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1279,9 +1283,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1319,7 +1323,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1425,7 +1429,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1567,7 +1571,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1597,28 +1601,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="32"/>
     </row>
     <row r="3" spans="1:27" ht="71.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:27" s="1" customFormat="1" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1786,7 +1790,7 @@
         <v>45713</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>55</v>
@@ -1804,10 +1808,10 @@
         <v>53</v>
       </c>
       <c r="I7" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="20" t="s">
         <v>67</v>
-      </c>
-      <c r="J7" s="20" t="s">
-        <v>68</v>
       </c>
       <c r="K7" s="22" t="s">
         <v>57</v>
@@ -1827,7 +1831,7 @@
         <v>64</v>
       </c>
       <c r="P7" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>59</v>
@@ -1856,16 +1860,16 @@
         <v>46078</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="F8" s="20" t="s">
         <v>72</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>73</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>63</v>
@@ -1874,16 +1878,16 @@
         <v>53</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="K8" s="25" t="s">
+      <c r="L8" s="25" t="s">
         <v>76</v>
-      </c>
-      <c r="L8" s="25" t="s">
-        <v>77</v>
       </c>
       <c r="M8" s="2">
         <v>2415</v>
@@ -1892,26 +1896,26 @@
         <v>1812</v>
       </c>
       <c r="O8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P8" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="P8" s="20" t="s">
+      <c r="Q8" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="R8" s="2"/>
       <c r="S8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="V8" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="W8" s="2"/>
       <c r="X8" s="2" t="s">
@@ -1921,95 +1925,95 @@
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:27" s="35" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B9" s="36">
+        <v>101</v>
+      </c>
+      <c r="B9" s="24">
         <v>46254</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="J9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K9" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="L9" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="H9" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="J9" s="37" t="s">
+      <c r="M9" s="2">
+        <v>5362</v>
+      </c>
+      <c r="N9" s="2">
+        <v>5362</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K9" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="L9" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="M9" s="37">
-        <v>5362</v>
-      </c>
-      <c r="N9" s="37">
-        <v>5362</v>
-      </c>
-      <c r="O9" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="P9" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q9" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="R9" s="37"/>
-      <c r="S9" s="40" t="s">
+      <c r="R9" s="2"/>
+      <c r="S9" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="T9" s="40" t="s">
+      <c r="T9" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U9" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="V9" s="37"/>
-      <c r="W9" s="37"/>
-      <c r="X9" s="37" t="s">
+      <c r="U9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="Y9" s="37"/>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="37"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
     </row>
     <row r="10" spans="1:27" ht="120" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B10" s="24">
         <v>46254</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>63</v>
@@ -2018,16 +2022,16 @@
         <v>53</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K10" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="K10" s="25" t="s">
-        <v>95</v>
-      </c>
       <c r="L10" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M10" s="2">
         <v>5362</v>
@@ -2036,10 +2040,10 @@
         <v>5362</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>60</v>
@@ -2052,7 +2056,7 @@
         <v>61</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
@@ -2063,95 +2067,95 @@
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
     </row>
-    <row r="11" spans="1:27" s="35" customFormat="1" ht="165" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="165" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="36">
+        <v>101</v>
+      </c>
+      <c r="B11" s="24">
         <v>46254</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="K11" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="D11" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="F11" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="G11" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="H11" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="I11" s="37" t="s">
+      <c r="L11" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="M11" s="2">
+        <v>5362</v>
+      </c>
+      <c r="N11" s="2">
+        <v>5362</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q11" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J11" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="K11" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="L11" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="M11" s="37">
-        <v>5362</v>
-      </c>
-      <c r="N11" s="37">
-        <v>5362</v>
-      </c>
-      <c r="O11" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="P11" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q11" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="R11" s="37"/>
-      <c r="S11" s="40" t="s">
+      <c r="R11" s="2"/>
+      <c r="S11" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="T11" s="40" t="s">
+      <c r="T11" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U11" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="V11" s="37"/>
-      <c r="W11" s="37"/>
-      <c r="X11" s="37" t="s">
+      <c r="U11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="Y11" s="37"/>
-      <c r="Z11" s="37"/>
-      <c r="AA11" s="37"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+      <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="135" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B12" s="24">
         <v>46254</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>63</v>
@@ -2160,16 +2164,16 @@
         <v>53</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K12" s="27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L12" s="27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M12" s="2">
         <v>5362</v>
@@ -2178,13 +2182,13 @@
         <v>5362</v>
       </c>
       <c r="O12" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="R12" s="2"/>
       <c r="S12" s="20" t="s">
@@ -2194,7 +2198,7 @@
         <v>61</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
@@ -2207,22 +2211,22 @@
     </row>
     <row r="13" spans="1:27" ht="195" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B13" s="24">
         <v>46254</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>63</v>
@@ -2231,16 +2235,16 @@
         <v>53</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="K13" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="L13" s="27" t="s">
         <v>115</v>
-      </c>
-      <c r="K13" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="L13" s="27" t="s">
-        <v>118</v>
       </c>
       <c r="M13" s="2">
         <v>5362</v>
@@ -2249,13 +2253,13 @@
         <v>5362</v>
       </c>
       <c r="O13" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P13" s="20" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R13" s="2"/>
       <c r="S13" s="20" t="s">
@@ -2265,7 +2269,7 @@
         <v>61</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
@@ -2278,22 +2282,22 @@
     </row>
     <row r="14" spans="1:27" ht="180" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B14" s="24">
         <v>46254</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="E14" s="20" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>63</v>
@@ -2302,16 +2306,16 @@
         <v>53</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="L14" s="27" t="s">
         <v>121</v>
-      </c>
-      <c r="K14" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="L14" s="27" t="s">
-        <v>124</v>
       </c>
       <c r="M14" s="2">
         <v>5362</v>
@@ -2320,13 +2324,13 @@
         <v>5362</v>
       </c>
       <c r="O14" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="R14" s="2"/>
       <c r="S14" s="20" t="s">
@@ -2336,7 +2340,7 @@
         <v>61</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
@@ -2349,22 +2353,22 @@
     </row>
     <row r="15" spans="1:27" ht="165" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B15" s="24">
         <v>46254</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>63</v>
@@ -2373,16 +2377,16 @@
         <v>53</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M15" s="2">
         <v>5362</v>
@@ -2391,13 +2395,13 @@
         <v>5362</v>
       </c>
       <c r="O15" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="R15" s="2"/>
       <c r="S15" s="20" t="s">
@@ -2407,7 +2411,7 @@
         <v>61</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
@@ -2420,22 +2424,22 @@
     </row>
     <row r="16" spans="1:27" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B16" s="24">
         <v>46254</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="E16" s="20" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>63</v>
@@ -2444,16 +2448,16 @@
         <v>53</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J16" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K16" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="K16" s="27" t="s">
-        <v>138</v>
-      </c>
       <c r="L16" s="27" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M16" s="2">
         <v>5362</v>
@@ -2462,10 +2466,10 @@
         <v>5362</v>
       </c>
       <c r="O16" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>60</v>
@@ -2478,7 +2482,7 @@
         <v>61</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
@@ -2491,22 +2495,22 @@
     </row>
     <row r="17" spans="1:27" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B17" s="24">
         <v>46254</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="E17" s="20" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>63</v>
@@ -2515,16 +2519,16 @@
         <v>53</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J17" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K17" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="L17" s="27" t="s">
         <v>141</v>
-      </c>
-      <c r="K17" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="L17" s="27" t="s">
-        <v>144</v>
       </c>
       <c r="M17" s="2">
         <v>5362</v>
@@ -2533,10 +2537,10 @@
         <v>5362</v>
       </c>
       <c r="O17" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>60</v>
@@ -2549,7 +2553,7 @@
         <v>61</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
@@ -2562,22 +2566,22 @@
     </row>
     <row r="18" spans="1:27" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B18" s="24">
         <v>46254</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="E18" s="20" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>63</v>
@@ -2586,16 +2590,16 @@
         <v>53</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K18" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="K18" s="27" t="s">
-        <v>150</v>
-      </c>
       <c r="L18" s="27" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="M18" s="2">
         <v>5362</v>
@@ -2604,13 +2608,13 @@
         <v>5362</v>
       </c>
       <c r="O18" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R18" s="2"/>
       <c r="S18" s="20" t="s">
@@ -2620,7 +2624,7 @@
         <v>61</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V18" s="2"/>
       <c r="W18" s="2"/>
@@ -2633,22 +2637,22 @@
     </row>
     <row r="19" spans="1:27" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B19" s="24">
         <v>46254</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="E19" s="20" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>63</v>
@@ -2657,16 +2661,16 @@
         <v>53</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="L19" s="27" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="M19" s="2">
         <v>5362</v>
@@ -2675,10 +2679,10 @@
         <v>5362</v>
       </c>
       <c r="O19" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>60</v>
@@ -2691,7 +2695,7 @@
         <v>61</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
@@ -2704,22 +2708,22 @@
     </row>
     <row r="20" spans="1:27" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B20" s="24">
         <v>46254</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="E20" s="20" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>63</v>
@@ -2728,16 +2732,16 @@
         <v>53</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="K20" s="27" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="L20" s="27" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M20" s="2">
         <v>5362</v>
@@ -2746,13 +2750,13 @@
         <v>5362</v>
       </c>
       <c r="O20" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R20" s="2"/>
       <c r="S20" s="20" t="s">
@@ -2762,7 +2766,7 @@
         <v>61</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
@@ -2775,22 +2779,22 @@
     </row>
     <row r="21" spans="1:27" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B21" s="24">
         <v>46254</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="E21" s="20" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>63</v>
@@ -2799,16 +2803,16 @@
         <v>53</v>
       </c>
       <c r="I21" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K21" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="K21" s="27" t="s">
-        <v>187</v>
-      </c>
       <c r="L21" s="27" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="M21" s="2">
         <v>5362</v>
@@ -2817,13 +2821,13 @@
         <v>5362</v>
       </c>
       <c r="O21" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R21" s="2"/>
       <c r="S21" s="20" t="s">
@@ -2833,7 +2837,7 @@
         <v>61</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V21" s="2"/>
       <c r="W21" s="2"/>
@@ -2846,22 +2850,22 @@
     </row>
     <row r="22" spans="1:27" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B22" s="24">
         <v>46254</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E22" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>192</v>
-      </c>
       <c r="F22" s="20" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>63</v>
@@ -2870,16 +2874,16 @@
         <v>53</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="K22" s="27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L22" s="27" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M22" s="2">
         <v>5362</v>
@@ -2888,13 +2892,13 @@
         <v>5362</v>
       </c>
       <c r="O22" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R22" s="2"/>
       <c r="S22" s="20" t="s">
@@ -2904,7 +2908,7 @@
         <v>61</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V22" s="2"/>
       <c r="W22" s="2"/>
@@ -2917,22 +2921,22 @@
     </row>
     <row r="23" spans="1:27" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B23" s="24">
         <v>46254</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="E23" s="20" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>63</v>
@@ -2941,16 +2945,16 @@
         <v>53</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L23" s="27" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M23" s="2">
         <v>5362</v>
@@ -2959,13 +2963,13 @@
         <v>5362</v>
       </c>
       <c r="O23" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R23" s="2"/>
       <c r="S23" s="20" t="s">
@@ -2975,7 +2979,7 @@
         <v>61</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
@@ -3249,6 +3253,24 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="edb9d0e4-5370-4cfb-9e4e-bdf6de379f60" xsi:nil="true"/>
+    <SharedWithUsers xmlns="bc464197-6a6a-4722-a0be-b24c34e3dd9e">
+      <UserInfo>
+        <DisplayName>Samantha Berman</DisplayName>
+        <AccountId>50</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b8c92ccb-f7f9-43b8-b828-8634382970d0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010071FB26ED47B7A040B9694E280C8A028C" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="51694721c5993bd1d7ee31732747c74d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b8c92ccb-f7f9-43b8-b828-8634382970d0" xmlns:ns3="bc464197-6a6a-4722-a0be-b24c34e3dd9e" xmlns:ns4="edb9d0e4-5370-4cfb-9e4e-bdf6de379f60" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2abadf83116fb303de7750466b9c1ce8" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b8c92ccb-f7f9-43b8-b828-8634382970d0"/>
@@ -3502,24 +3524,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="edb9d0e4-5370-4cfb-9e4e-bdf6de379f60" xsi:nil="true"/>
-    <SharedWithUsers xmlns="bc464197-6a6a-4722-a0be-b24c34e3dd9e">
-      <UserInfo>
-        <DisplayName>Samantha Berman</DisplayName>
-        <AccountId>50</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b8c92ccb-f7f9-43b8-b828-8634382970d0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3530,6 +3534,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B64A78E-FA98-4BD6-A16D-D65CD3857185}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="edb9d0e4-5370-4cfb-9e4e-bdf6de379f60"/>
+    <ds:schemaRef ds:uri="bc464197-6a6a-4722-a0be-b24c34e3dd9e"/>
+    <ds:schemaRef ds:uri="b8c92ccb-f7f9-43b8-b828-8634382970d0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04EE2F2F-2877-498F-B100-D17CB7202974}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3549,18 +3565,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B64A78E-FA98-4BD6-A16D-D65CD3857185}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="edb9d0e4-5370-4cfb-9e4e-bdf6de379f60"/>
-    <ds:schemaRef ds:uri="bc464197-6a6a-4722-a0be-b24c34e3dd9e"/>
-    <ds:schemaRef ds:uri="b8c92ccb-f7f9-43b8-b828-8634382970d0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8194028F-5AB4-417F-915C-72EAB37A02CF}">
   <ds:schemaRefs>

--- a/assets/data/search_methods/ukllc_catalogue/File_2_Documentation_Master.xlsx
+++ b/assets/data/search_methods/ukllc_catalogue/File_2_Documentation_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UCL\Github\OWL\assets\data\search_methods\ukllc_catalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D494034-B940-4926-A6DB-13F4C12BB4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64545F3D-5ED1-44E4-A7FD-160CFA0E0DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37620" yWindow="720" windowWidth="26130" windowHeight="15480" xr2:uid="{BF5C6858-8849-464B-BFFF-EA4DD55D1A19}"/>
+    <workbookView xWindow="-37620" yWindow="0" windowWidth="26130" windowHeight="15480" xr2:uid="{BF5C6858-8849-464B-BFFF-EA4DD55D1A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="193">
   <si>
     <r>
       <rPr>
@@ -459,45 +459,15 @@
     <t>APOE,  rs7413,  rs429358, Genetics, DNA</t>
   </si>
   <si>
-    <t>NSHD46_2023_Cost_of_Living_v0001_20260218.csv</t>
-  </si>
-  <si>
-    <t>2023 Cost of Living Questionnaire</t>
-  </si>
-  <si>
-    <t>Short questionnaire was sent to all active participants in 2023 (age 77 years). The questionnaire was asked to investigate if changes to the cost of living was having an impact on participants financial situation. It also asked questions on physical and mental health to find out if this was being impacted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questionnaire asked at age 77 years (2023) to find out the impact of changes to the cost of living to participants financial circumstances, as well as their mental and physical health. </t>
-  </si>
-  <si>
-    <t>NSHD46_2023_Cost_of_Living_v0001_values_20260218.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_2023_Cost_of_Living_v0001_description_20260218.csv</t>
-  </si>
-  <si>
-    <t>04/2023</t>
-  </si>
-  <si>
-    <t>05/2023</t>
-  </si>
-  <si>
     <t xml:space="preserve">All active study participants </t>
   </si>
   <si>
-    <t>Financial circumstances, mental health, physical health</t>
-  </si>
-  <si>
     <t>Yes - low cell counts</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>agecl23x</t>
-  </si>
-  <si>
     <t>NSHD46_CAT-2011_Blood_Biochemistry_v0001_description_20260812.csv</t>
   </si>
   <si>
@@ -852,13 +822,13 @@
     <t>housing, household, accomadation, children, grandchildren, vehicles, pets</t>
   </si>
   <si>
-    <t>NSHD46_APOE_v0001_2026022.csv</t>
-  </si>
-  <si>
     <t>NSHD46_CAT-2011_Blood_Biochemistry_v0001_20260814.csv</t>
   </si>
   <si>
     <t>NSHD46_CAT-1103_BP_v0001_20260814.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_APOE_v0001_20260422.csv</t>
   </si>
 </sst>
 </file>
@@ -1579,7 +1549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5527E288-64E3-40B9-871A-CF28D789BFEF}">
-  <dimension ref="A2:AA32"/>
+  <dimension ref="A2:AA31"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -1790,7 +1760,7 @@
         <v>45713</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>55</v>
@@ -1856,20 +1826,23 @@
       <c r="AA7" s="20"/>
     </row>
     <row r="8" spans="1:27" ht="105" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>91</v>
+      </c>
       <c r="B8" s="24">
-        <v>46078</v>
+        <v>46254</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>69</v>
+        <v>190</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>72</v>
+        <v>75</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>78</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>63</v>
@@ -1881,42 +1854,40 @@
         <v>73</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="L8" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8" s="2">
+        <v>5362</v>
+      </c>
+      <c r="N8" s="2">
+        <v>5362</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K8" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="L8" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="M8" s="2">
-        <v>2415</v>
-      </c>
-      <c r="N8" s="2">
-        <v>1812</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="P8" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="R8" s="2"/>
-      <c r="S8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>80</v>
+      <c r="S8" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="T8" s="20" t="s">
+        <v>61</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>81</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2" t="s">
         <v>54</v>
@@ -1925,24 +1896,24 @@
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:27" ht="105" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="120" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B9" s="24">
         <v>46254</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>88</v>
+        <v>80</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>139</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>63</v>
@@ -1951,16 +1922,16 @@
         <v>53</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="K9" s="25" t="s">
-        <v>86</v>
-      </c>
       <c r="L9" s="25" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="M9" s="2">
         <v>5362</v>
@@ -1969,13 +1940,13 @@
         <v>5362</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="R9" s="2"/>
       <c r="S9" s="20" t="s">
@@ -1985,7 +1956,7 @@
         <v>61</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
@@ -1996,24 +1967,24 @@
       <c r="Z9" s="2"/>
       <c r="AA9" s="2"/>
     </row>
-    <row r="10" spans="1:27" ht="120" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="165" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B10" s="24">
         <v>46254</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>89</v>
+        <v>191</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>63</v>
@@ -2022,16 +1993,16 @@
         <v>53</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="K10" s="25" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="L10" s="25" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="M10" s="2">
         <v>5362</v>
@@ -2040,13 +2011,13 @@
         <v>5362</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="R10" s="2"/>
       <c r="S10" s="20" t="s">
@@ -2056,7 +2027,7 @@
         <v>61</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
@@ -2067,24 +2038,24 @@
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
     </row>
-    <row r="11" spans="1:27" ht="165" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="135" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B11" s="24">
         <v>46254</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>96</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>63</v>
@@ -2093,16 +2064,16 @@
         <v>53</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K11" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" s="27" t="s">
         <v>98</v>
-      </c>
-      <c r="L11" s="25" t="s">
-        <v>87</v>
       </c>
       <c r="M11" s="2">
         <v>5362</v>
@@ -2110,14 +2081,14 @@
       <c r="N11" s="2">
         <v>5362</v>
       </c>
-      <c r="O11" s="2" t="s">
-        <v>77</v>
+      <c r="O11" s="26" t="s">
+        <v>69</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>99</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="R11" s="2"/>
       <c r="S11" s="20" t="s">
@@ -2127,7 +2098,7 @@
         <v>61</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
@@ -2138,24 +2109,24 @@
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
     </row>
-    <row r="12" spans="1:27" ht="135" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>101</v>
+    <row r="12" spans="1:27" ht="195" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
+        <v>91</v>
       </c>
       <c r="B12" s="24">
         <v>46254</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>106</v>
+        <v>100</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>63</v>
@@ -2164,16 +2135,16 @@
         <v>53</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K12" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K12" s="27" t="s">
-        <v>98</v>
-      </c>
       <c r="L12" s="27" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="M12" s="2">
         <v>5362</v>
@@ -2182,13 +2153,13 @@
         <v>5362</v>
       </c>
       <c r="O12" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>109</v>
+        <v>69</v>
+      </c>
+      <c r="P12" s="20" t="s">
+        <v>106</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="R12" s="2"/>
       <c r="S12" s="20" t="s">
@@ -2198,7 +2169,7 @@
         <v>61</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
@@ -2209,24 +2180,24 @@
       <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
     </row>
-    <row r="13" spans="1:27" ht="195" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="180" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B13" s="24">
         <v>46254</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="E13" s="20" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>63</v>
@@ -2235,16 +2206,16 @@
         <v>53</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="M13" s="2">
         <v>5362</v>
@@ -2253,13 +2224,13 @@
         <v>5362</v>
       </c>
       <c r="O13" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="P13" s="20" t="s">
-        <v>116</v>
+        <v>69</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="R13" s="2"/>
       <c r="S13" s="20" t="s">
@@ -2269,7 +2240,7 @@
         <v>61</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
@@ -2280,24 +2251,24 @@
       <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
     </row>
-    <row r="14" spans="1:27" ht="180" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
-        <v>101</v>
+    <row r="14" spans="1:27" ht="165" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>120</v>
       </c>
       <c r="B14" s="24">
         <v>46254</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>63</v>
@@ -2306,16 +2277,16 @@
         <v>53</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K14" s="27" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="L14" s="27" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="M14" s="2">
         <v>5362</v>
@@ -2324,13 +2295,13 @@
         <v>5362</v>
       </c>
       <c r="O14" s="26" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="R14" s="2"/>
       <c r="S14" s="20" t="s">
@@ -2340,7 +2311,7 @@
         <v>61</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
@@ -2351,24 +2322,24 @@
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
     </row>
-    <row r="15" spans="1:27" ht="165" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B15" s="24">
         <v>46254</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>63</v>
@@ -2377,16 +2348,16 @@
         <v>53</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="M15" s="2">
         <v>5362</v>
@@ -2395,13 +2366,13 @@
         <v>5362</v>
       </c>
       <c r="O15" s="26" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="R15" s="2"/>
       <c r="S15" s="20" t="s">
@@ -2411,7 +2382,7 @@
         <v>61</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
@@ -2422,24 +2393,24 @@
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
     </row>
-    <row r="16" spans="1:27" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B16" s="24">
         <v>46254</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>63</v>
@@ -2448,16 +2419,16 @@
         <v>53</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K16" s="27" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="L16" s="27" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="M16" s="2">
         <v>5362</v>
@@ -2466,10 +2437,10 @@
         <v>5362</v>
       </c>
       <c r="O16" s="26" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>60</v>
@@ -2482,7 +2453,7 @@
         <v>61</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
@@ -2493,24 +2464,24 @@
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
     </row>
-    <row r="17" spans="1:27" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="B17" s="24">
         <v>46254</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>63</v>
@@ -2519,16 +2490,16 @@
         <v>53</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="M17" s="2">
         <v>5362</v>
@@ -2537,13 +2508,13 @@
         <v>5362</v>
       </c>
       <c r="O17" s="26" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R17" s="2"/>
       <c r="S17" s="20" t="s">
@@ -2553,7 +2524,7 @@
         <v>61</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
@@ -2564,24 +2535,24 @@
       <c r="Z17" s="2"/>
       <c r="AA17" s="2"/>
     </row>
-    <row r="18" spans="1:27" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B18" s="24">
         <v>46254</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>63</v>
@@ -2590,16 +2561,16 @@
         <v>53</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="K18" s="27" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="L18" s="27" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="M18" s="2">
         <v>5362</v>
@@ -2608,13 +2579,13 @@
         <v>5362</v>
       </c>
       <c r="O18" s="26" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="R18" s="2"/>
       <c r="S18" s="20" t="s">
@@ -2624,7 +2595,7 @@
         <v>61</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="V18" s="2"/>
       <c r="W18" s="2"/>
@@ -2635,24 +2606,24 @@
       <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
     </row>
-    <row r="19" spans="1:27" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B19" s="24">
         <v>46254</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F19" s="20" t="s">
         <v>165</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>166</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>63</v>
@@ -2661,16 +2632,16 @@
         <v>53</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="L19" s="27" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="M19" s="2">
         <v>5362</v>
@@ -2679,13 +2650,13 @@
         <v>5362</v>
       </c>
       <c r="O19" s="26" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R19" s="2"/>
       <c r="S19" s="20" t="s">
@@ -2695,7 +2666,7 @@
         <v>61</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
@@ -2706,24 +2677,24 @@
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
     </row>
-    <row r="20" spans="1:27" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B20" s="24">
         <v>46254</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="E20" s="20" t="s">
-        <v>178</v>
-      </c>
       <c r="F20" s="20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>63</v>
@@ -2732,16 +2703,16 @@
         <v>53</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K20" s="27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L20" s="27" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="M20" s="2">
         <v>5362</v>
@@ -2750,13 +2721,13 @@
         <v>5362</v>
       </c>
       <c r="O20" s="26" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="R20" s="2"/>
       <c r="S20" s="20" t="s">
@@ -2766,7 +2737,7 @@
         <v>61</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
@@ -2777,24 +2748,24 @@
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
     </row>
-    <row r="21" spans="1:27" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B21" s="24">
         <v>46254</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E21" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>183</v>
-      </c>
       <c r="F21" s="20" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>63</v>
@@ -2803,16 +2774,16 @@
         <v>53</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K21" s="27" t="s">
-        <v>184</v>
+        <v>88</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="M21" s="2">
         <v>5362</v>
@@ -2821,13 +2792,13 @@
         <v>5362</v>
       </c>
       <c r="O21" s="26" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="R21" s="2"/>
       <c r="S21" s="20" t="s">
@@ -2837,7 +2808,7 @@
         <v>61</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="V21" s="2"/>
       <c r="W21" s="2"/>
@@ -2848,24 +2819,24 @@
       <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
     </row>
-    <row r="22" spans="1:27" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B22" s="24">
         <v>46254</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="E22" s="20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>63</v>
@@ -2874,16 +2845,16 @@
         <v>53</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K22" s="27" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="L22" s="27" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="M22" s="2">
         <v>5362</v>
@@ -2892,13 +2863,13 @@
         <v>5362</v>
       </c>
       <c r="O22" s="26" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="R22" s="2"/>
       <c r="S22" s="20" t="s">
@@ -2908,7 +2879,7 @@
         <v>61</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="V22" s="2"/>
       <c r="W22" s="2"/>
@@ -2919,73 +2890,30 @@
       <c r="Z22" s="2"/>
       <c r="AA22" s="2"/>
     </row>
-    <row r="23" spans="1:27" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="24">
-        <v>46254</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="K23" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="L23" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="M23" s="2">
-        <v>5362</v>
-      </c>
-      <c r="N23" s="2">
-        <v>5362</v>
-      </c>
-      <c r="O23" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>79</v>
-      </c>
+    <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
-      <c r="S23" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T23" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="U23" s="2" t="s">
-        <v>80</v>
-      </c>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
-      <c r="X23" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="X23" s="2"/>
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
@@ -3213,34 +3141,6 @@
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
       <c r="AA31" s="2"/>
-    </row>
-    <row r="32" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
-      <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
-      <c r="W32" s="2"/>
-      <c r="X32" s="2"/>
-      <c r="Y32" s="2"/>
-      <c r="Z32" s="2"/>
-      <c r="AA32" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/assets/data/search_methods/ukllc_catalogue/File_2_Documentation_Master.xlsx
+++ b/assets/data/search_methods/ukllc_catalogue/File_2_Documentation_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UCL\Github\OWL\assets\data\search_methods\ukllc_catalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64545F3D-5ED1-44E4-A7FD-160CFA0E0DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A19617A-B0BA-40B1-8070-E4E3A142969E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37620" yWindow="0" windowWidth="26130" windowHeight="15480" xr2:uid="{BF5C6858-8849-464B-BFFF-EA4DD55D1A19}"/>
+    <workbookView xWindow="1170" yWindow="0" windowWidth="26130" windowHeight="15480" xr2:uid="{BF5C6858-8849-464B-BFFF-EA4DD55D1A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -528,9 +528,6 @@
     <t>Fine</t>
   </si>
   <si>
-    <t>NSHD46_CAT-51012_Cancer_v0001_20260812.csv</t>
-  </si>
-  <si>
     <t>NSHD46_CAT-51012_Cancer_v0001_description_20260812.csv</t>
   </si>
   <si>
@@ -552,9 +549,6 @@
     <t>Cancer, ICD</t>
   </si>
   <si>
-    <t>NSHD46_CAT-51021_Clin_disorder_v0001_20260812.csv</t>
-  </si>
-  <si>
     <t>Topic - Clinical disorders (category 51021)</t>
   </si>
   <si>
@@ -573,9 +567,6 @@
     <t>Clinical disorders, cardio, cerebo-vascular disease, hypertension, raised cholesterol, renal impairment, diabetes, obesity, hypothyroidism, hyperthyroidism, anaemia, respiratory disease, liver disease, psychiatric problems, cancer, atrial fibrillation, ECG, osteporosis.</t>
   </si>
   <si>
-    <t>NSHD46_CAT-51015_Endo_Metab_v0001_20260812.csv</t>
-  </si>
-  <si>
     <t>NSHD46_CAT-51015_Endo_Metab_v0001_description_20260812.csv</t>
   </si>
   <si>
@@ -597,9 +588,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>NSHD46_CAT-51014_Heart_Circ_v0001_20260812.csv</t>
-  </si>
-  <si>
     <t>Topic - Heart and circulatory conditions (category 51014)</t>
   </si>
   <si>
@@ -615,9 +603,6 @@
     <t>fine</t>
   </si>
   <si>
-    <t>NSHD46_CAT-51013_Respiratory_v0001_20260812.csv</t>
-  </si>
-  <si>
     <t>NSHD46_CAT-51013_Respiratory_v0001_description_20260812.csv</t>
   </si>
   <si>
@@ -633,9 +618,6 @@
     <t>respiratory, copd, asthma, hay fever, bronchitis, emphysema</t>
   </si>
   <si>
-    <t>NSHD46_CAT-5252_Alcohol_v0001_20260812.csv</t>
-  </si>
-  <si>
     <t>NSHD46_CAT-5252_Alcohol_v0001_description_20260812.csv</t>
   </si>
   <si>
@@ -651,9 +633,6 @@
     <t>alcohol, drinking, spirits, wine, beer, larger, cider, stout, liqueurs, drink</t>
   </si>
   <si>
-    <t>NSHD46_CAT-5251_Smoking_v0001_20260812.csv</t>
-  </si>
-  <si>
     <t>NSHD46_CAT-5251_Smoking_v0001_description_20260812.csv</t>
   </si>
   <si>
@@ -708,9 +687,6 @@
     <t>Data from the questionnaires on drinking alcohol i.e amount of alcohol drunk, drinking habits, others concerned about your drinking, feeling and mood after drinking.</t>
   </si>
   <si>
-    <t>NSHD46_CAT-5211_EPIC_v0001_20260812.csv</t>
-  </si>
-  <si>
     <t>NSHD46_CAT-5211_EPIC_v0001_description_20260812.csv</t>
   </si>
   <si>
@@ -732,9 +708,6 @@
     <t>EPAQ2, physical, activity, leisure, transportation, energy, expenditure, PAEE</t>
   </si>
   <si>
-    <t>NSHD46_CAT-5151_Econ_Circ_v0001_20260813.csv</t>
-  </si>
-  <si>
     <t>NSHD46_CAT-5151_Econ_Circ_v0001_description_20260813.csv</t>
   </si>
   <si>
@@ -759,9 +732,6 @@
     <t>Data on the economic circumstances of the participant such as personal and household income, hours worked including overtime, special payments, financial difficulties and benefit details. Information from spouse was also obtained. Questions were asked in 1972 (age 26 years),  1982 (age 36 years), 1989 (age 43 years), 1999 (age 53 years), 2006-10 (age 60-64 years), 2015 (age 69 years), 2023 (age 77 years) and 2025 (age 79 years).</t>
   </si>
   <si>
-    <t>NSHD46_CAT-5155_Education_v0001_20260813.csv</t>
-  </si>
-  <si>
     <t>NSHD46_CAT-5155_Education_v0001_description_20260813.csv</t>
   </si>
   <si>
@@ -780,9 +750,6 @@
     <t>education, qualification, training, school</t>
   </si>
   <si>
-    <t>NSHD46_CAT-5154_Emplymnt_Hist_v0001_20260813.csv</t>
-  </si>
-  <si>
     <t>NSHD46_CAT-5154_Emplymnt_Hist_v0001_description_20260813.csv</t>
   </si>
   <si>
@@ -801,9 +768,6 @@
     <t>employment, occupation, work, job, voluntary, retirement</t>
   </si>
   <si>
-    <t>NSHD46_CAT-5152_Household_v0001_20260813.csv</t>
-  </si>
-  <si>
     <t>NSHD46_CAT-5152_Household_v0001_description_20260813.csv</t>
   </si>
   <si>
@@ -822,13 +786,49 @@
     <t>housing, household, accomadation, children, grandchildren, vehicles, pets</t>
   </si>
   <si>
-    <t>NSHD46_CAT-2011_Blood_Biochemistry_v0001_20260814.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-1103_BP_v0001_20260814.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_APOE_v0001_20260422.csv</t>
+    <t>NSHD46_APOE_v0001_20260422</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-2011_Blood_Biochemistry_v0001_20260814</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-1103_BP_v0001_20260814</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51012_Cancer_v0001_20260812</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51021_Clin_disorder_v0001_20260812</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51015_Endo_Metab_v0001_20260812</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51014_Heart_Circ_v0001_20260812</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51013_Respiratory_v0001_20260812</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5252_Alcohol_v0001_20260812</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5251_Smoking_v0001_20260812</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5211_EPIC_v0001_20260812</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5151_Econ_Circ_v0001_20260813</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5155_Education_v0001_20260813</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5154_Emplymnt_Hist_v0001_20260813</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5152_Household_v0001_20260813</t>
   </si>
 </sst>
 </file>
@@ -1760,7 +1760,7 @@
         <v>45713</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>55</v>
@@ -1833,7 +1833,7 @@
         <v>46254</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>75</v>
@@ -1910,10 +1910,10 @@
         <v>80</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>63</v>
@@ -1975,16 +1975,16 @@
         <v>46254</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E10" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="F10" s="20" t="s">
         <v>140</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>147</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>63</v>
@@ -2046,16 +2046,16 @@
         <v>46254</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>92</v>
+        <v>181</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>63</v>
@@ -2064,16 +2064,16 @@
         <v>53</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K11" s="27" t="s">
         <v>88</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M11" s="2">
         <v>5362</v>
@@ -2085,10 +2085,10 @@
         <v>69</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R11" s="2"/>
       <c r="S11" s="20" t="s">
@@ -2117,16 +2117,16 @@
         <v>46254</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>100</v>
+        <v>182</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>63</v>
@@ -2135,16 +2135,16 @@
         <v>53</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K12" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="L12" s="27" t="s">
         <v>103</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K12" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="L12" s="27" t="s">
-        <v>105</v>
       </c>
       <c r="M12" s="2">
         <v>5362</v>
@@ -2156,7 +2156,7 @@
         <v>69</v>
       </c>
       <c r="P12" s="20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>70</v>
@@ -2188,16 +2188,16 @@
         <v>46254</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="E13" s="20" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>63</v>
@@ -2206,16 +2206,16 @@
         <v>53</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K13" s="27" t="s">
         <v>88</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M13" s="2">
         <v>5362</v>
@@ -2227,10 +2227,10 @@
         <v>69</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="R13" s="2"/>
       <c r="S13" s="20" t="s">
@@ -2253,22 +2253,22 @@
     </row>
     <row r="14" spans="1:27" ht="165" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B14" s="24">
         <v>46254</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>63</v>
@@ -2277,16 +2277,16 @@
         <v>53</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K14" s="27" t="s">
         <v>88</v>
       </c>
       <c r="L14" s="27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M14" s="2">
         <v>5362</v>
@@ -2298,10 +2298,10 @@
         <v>69</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R14" s="2"/>
       <c r="S14" s="20" t="s">
@@ -2324,22 +2324,22 @@
     </row>
     <row r="15" spans="1:27" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B15" s="24">
         <v>46254</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>63</v>
@@ -2348,16 +2348,16 @@
         <v>53</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M15" s="2">
         <v>5362</v>
@@ -2369,7 +2369,7 @@
         <v>69</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>60</v>
@@ -2395,22 +2395,22 @@
     </row>
     <row r="16" spans="1:27" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B16" s="24">
         <v>46254</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>63</v>
@@ -2419,16 +2419,16 @@
         <v>53</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K16" s="27" t="s">
         <v>88</v>
       </c>
       <c r="L16" s="27" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="M16" s="2">
         <v>5362</v>
@@ -2440,7 +2440,7 @@
         <v>69</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>60</v>
@@ -2453,7 +2453,7 @@
         <v>61</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
@@ -2472,16 +2472,16 @@
         <v>46254</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>63</v>
@@ -2490,16 +2490,16 @@
         <v>53</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="M17" s="2">
         <v>5362</v>
@@ -2511,7 +2511,7 @@
         <v>69</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>70</v>
@@ -2543,16 +2543,16 @@
         <v>46254</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="E18" s="20" t="s">
-        <v>164</v>
-      </c>
       <c r="F18" s="20" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>63</v>
@@ -2561,16 +2561,16 @@
         <v>53</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="K18" s="27" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L18" s="27" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="M18" s="2">
         <v>5362</v>
@@ -2582,7 +2582,7 @@
         <v>69</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>60</v>
@@ -2614,16 +2614,16 @@
         <v>46254</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>63</v>
@@ -2632,16 +2632,16 @@
         <v>53</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="L19" s="27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M19" s="2">
         <v>5362</v>
@@ -2653,7 +2653,7 @@
         <v>69</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>70</v>
@@ -2685,16 +2685,16 @@
         <v>46254</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>63</v>
@@ -2703,16 +2703,16 @@
         <v>53</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="K20" s="27" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="L20" s="27" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="M20" s="2">
         <v>5362</v>
@@ -2724,7 +2724,7 @@
         <v>69</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>70</v>
@@ -2756,16 +2756,16 @@
         <v>46254</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>63</v>
@@ -2774,16 +2774,16 @@
         <v>53</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="K21" s="27" t="s">
         <v>88</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M21" s="2">
         <v>5362</v>
@@ -2795,7 +2795,7 @@
         <v>69</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>70</v>
@@ -2827,16 +2827,16 @@
         <v>46254</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>63</v>
@@ -2845,16 +2845,16 @@
         <v>53</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="K22" s="27" t="s">
         <v>83</v>
       </c>
       <c r="L22" s="27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M22" s="2">
         <v>5362</v>
@@ -2866,7 +2866,7 @@
         <v>69</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>70</v>
@@ -3171,6 +3171,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010071FB26ED47B7A040B9694E280C8A028C" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="51694721c5993bd1d7ee31732747c74d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b8c92ccb-f7f9-43b8-b828-8634382970d0" xmlns:ns3="bc464197-6a6a-4722-a0be-b24c34e3dd9e" xmlns:ns4="edb9d0e4-5370-4cfb-9e4e-bdf6de379f60" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2abadf83116fb303de7750466b9c1ce8" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b8c92ccb-f7f9-43b8-b828-8634382970d0"/>
@@ -3424,15 +3433,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B64A78E-FA98-4BD6-A16D-D65CD3857185}">
   <ds:schemaRefs>
@@ -3446,6 +3446,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8194028F-5AB4-417F-915C-72EAB37A02CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04EE2F2F-2877-498F-B100-D17CB7202974}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3463,12 +3471,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8194028F-5AB4-417F-915C-72EAB37A02CF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/assets/data/search_methods/ukllc_catalogue/File_2_Documentation_Master.xlsx
+++ b/assets/data/search_methods/ukllc_catalogue/File_2_Documentation_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UCL\Github\OWL\assets\data\search_methods\ukllc_catalogue\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Q:\rmjdish\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A19617A-B0BA-40B1-8070-E4E3A142969E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFE931D-FC03-4B59-98E0-908BDC6BEE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="0" windowWidth="26130" windowHeight="15480" xr2:uid="{BF5C6858-8849-464B-BFFF-EA4DD55D1A19}"/>
+    <workbookView xWindow="2205" yWindow="0" windowWidth="18000" windowHeight="15600" xr2:uid="{BF5C6858-8849-464B-BFFF-EA4DD55D1A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="191">
   <si>
     <r>
       <rPr>
@@ -468,12 +457,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>NSHD46_CAT-2011_Blood_Biochemistry_v0001_description_20260812.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-2011_Blood_Biochemistry_v0001_values_20260812.csv</t>
-  </si>
-  <si>
     <t>Yes - Date information</t>
   </si>
   <si>
@@ -489,18 +472,9 @@
     <t>A range of key biochemistry markers were measured in the blood samples collected at 1999 (at age 53 years) and repeated at 2006-2010 (at age 60-64 years), 2015 (age 69 years) and 2023 (age 77 years).</t>
   </si>
   <si>
-    <t>NSHD46_CAT-11021_Anthropometry_v0001_20260812</t>
-  </si>
-  <si>
     <t>Topic - Anthropometry (Category 11021)</t>
   </si>
   <si>
-    <t>NSHD46_CAT-11021_Anthropometry_v0001_description_20260812.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-11021_Anthropometry_v0001_values_20260812.csv</t>
-  </si>
-  <si>
     <t>03/1946</t>
   </si>
   <si>
@@ -510,12 +484,6 @@
     <t>height, weight, body mass index (bmi), physical measures</t>
   </si>
   <si>
-    <t>NSHD46_CAT-1103_BP_v0001_description_20260812.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-1103_BP_v0001_values_20260812.csv</t>
-  </si>
-  <si>
     <t>01/1982</t>
   </si>
   <si>
@@ -525,15 +493,6 @@
     <t>Yes - Text variable</t>
   </si>
   <si>
-    <t>Fine</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-51012_Cancer_v0001_description_20260812.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-51012_Cancer_v0001_values_20260812.csv</t>
-  </si>
-  <si>
     <t>Topic - Blood Pressure (Category 1103)</t>
   </si>
   <si>
@@ -552,12 +511,6 @@
     <t>Topic - Clinical disorders (category 51021)</t>
   </si>
   <si>
-    <t>NSHD46_CAT-51021_Clin_disorder_v0001_description_20260812.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-51021_Clin_disorder_v0001_values_20260812.csv</t>
-  </si>
-  <si>
     <t>01/2006</t>
   </si>
   <si>
@@ -567,12 +520,6 @@
     <t>Clinical disorders, cardio, cerebo-vascular disease, hypertension, raised cholesterol, renal impairment, diabetes, obesity, hypothyroidism, hyperthyroidism, anaemia, respiratory disease, liver disease, psychiatric problems, cancer, atrial fibrillation, ECG, osteporosis.</t>
   </si>
   <si>
-    <t>NSHD46_CAT-51015_Endo_Metab_v0001_description_20260812.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-51015_Endo_Metab_v0001_values_20260812.csv</t>
-  </si>
-  <si>
     <t>Topic - Endocrine and metabolic conditions (category 51015)</t>
   </si>
   <si>
@@ -591,24 +538,9 @@
     <t>Topic - Heart and circulatory conditions (category 51014)</t>
   </si>
   <si>
-    <t>NSHD46_CAT-51014_Heart_Circ_v0001_description_20260812.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-51014_Heart_Circ_v0001_values_20260812.csv</t>
-  </si>
-  <si>
     <t xml:space="preserve">heart, circulatory, cardiovascular, attacks, failure, pulmonary, embolism, stroke, varicose veins, angina, chest </t>
   </si>
   <si>
-    <t>fine</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-51013_Respiratory_v0001_description_20260812.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-51013_Respiratory_v0001_values_20260812.csv</t>
-  </si>
-  <si>
     <t>Topic - Repiratory conditions (category 51013)</t>
   </si>
   <si>
@@ -618,12 +550,6 @@
     <t>respiratory, copd, asthma, hay fever, bronchitis, emphysema</t>
   </si>
   <si>
-    <t>NSHD46_CAT-5252_Alcohol_v0001_description_20260812.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-5252_Alcohol_v0001_values_20260812.csv</t>
-  </si>
-  <si>
     <t>Topic - Alcohol (category 5252)</t>
   </si>
   <si>
@@ -633,12 +559,6 @@
     <t>alcohol, drinking, spirits, wine, beer, larger, cider, stout, liqueurs, drink</t>
   </si>
   <si>
-    <t>NSHD46_CAT-5251_Smoking_v0001_description_20260812.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-5251_Smoking_v0001_values_20260812.csv</t>
-  </si>
-  <si>
     <t>Topic - Smoking (category 5251)</t>
   </si>
   <si>
@@ -687,12 +607,6 @@
     <t>Data from the questionnaires on drinking alcohol i.e amount of alcohol drunk, drinking habits, others concerned about your drinking, feeling and mood after drinking.</t>
   </si>
   <si>
-    <t>NSHD46_CAT-5211_EPIC_v0001_description_20260812.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-5211_EPIC_v0001_values_20260812.csv</t>
-  </si>
-  <si>
     <t>Topic - EPIC Physical activity questionnaire (category 5211)</t>
   </si>
   <si>
@@ -708,12 +622,6 @@
     <t>EPAQ2, physical, activity, leisure, transportation, energy, expenditure, PAEE</t>
   </si>
   <si>
-    <t>NSHD46_CAT-5151_Econ_Circ_v0001_description_20260813.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-5151_Econ_Circ_v0001_values_20260813.csv</t>
-  </si>
-  <si>
     <t>Topic - Economic circumstances (category 5151)</t>
   </si>
   <si>
@@ -732,12 +640,6 @@
     <t>Data on the economic circumstances of the participant such as personal and household income, hours worked including overtime, special payments, financial difficulties and benefit details. Information from spouse was also obtained. Questions were asked in 1972 (age 26 years),  1982 (age 36 years), 1989 (age 43 years), 1999 (age 53 years), 2006-10 (age 60-64 years), 2015 (age 69 years), 2023 (age 77 years) and 2025 (age 79 years).</t>
   </si>
   <si>
-    <t>NSHD46_CAT-5155_Education_v0001_description_20260813.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-5155_Education_v0001_values_20260813.csv</t>
-  </si>
-  <si>
     <t>Topic - Education (category 5155)</t>
   </si>
   <si>
@@ -750,12 +652,6 @@
     <t>education, qualification, training, school</t>
   </si>
   <si>
-    <t>NSHD46_CAT-5154_Emplymnt_Hist_v0001_description_20260813.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-5154_Emplymnt_Hist_v0001_values_20260813.csv</t>
-  </si>
-  <si>
     <t>This category contains data on the employment history which includes voluntary work and retirement. Details captured included, number of hours works , overtime, manegerial duties,  occupational codes. Similar information is available for the spouse. Questions were asked in 1982 (age 36 years), 1989 (age 43 years), 1999 (age 53 years), 2006-10 (age 60-64 years), 2014 (age 68 years), 2015 (age 69 years), 2022 (age 76 years) and 2025 (age 79 years).</t>
   </si>
   <si>
@@ -768,12 +664,6 @@
     <t>employment, occupation, work, job, voluntary, retirement</t>
   </si>
   <si>
-    <t>NSHD46_CAT-5152_Household_v0001_description_20260813.csv</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-5152_Household_v0001_values_20260813.csv</t>
-  </si>
-  <si>
     <t>Topic - Household (category 5152)</t>
   </si>
   <si>
@@ -789,46 +679,139 @@
     <t>NSHD46_APOE_v0001_20260422</t>
   </si>
   <si>
-    <t>NSHD46_CAT-2011_Blood_Biochemistry_v0001_20260814</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-1103_BP_v0001_20260814</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-51012_Cancer_v0001_20260812</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-51021_Clin_disorder_v0001_20260812</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-51015_Endo_Metab_v0001_20260812</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-51014_Heart_Circ_v0001_20260812</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-51013_Respiratory_v0001_20260812</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-5252_Alcohol_v0001_20260812</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-5251_Smoking_v0001_20260812</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-5211_EPIC_v0001_20260812</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-5151_Econ_Circ_v0001_20260813</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-5155_Education_v0001_20260813</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-5154_Emplymnt_Hist_v0001_20260813</t>
-  </si>
-  <si>
-    <t>NSHD46_CAT-5152_Household_v0001_20260813</t>
+    <t>NSHD46_CAT-2011_Blood_Biochemistry_v0001_20260907</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-2011_Blood_Biochemistry_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-2011_Blood_Biochemistry_v0001_description_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-11021_Anthropometry_v0001_20260907</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-11021_Anthropometry_v0001_description_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-11021_Anthropometry_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-1103_BP_v0001_20260907</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-1103_BP_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-1103_BP_v0001_description_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51012_Cancer_v0001_20260907</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51012_Cancer_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51012_Cancer_v0001_description_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51021_Clin_disorder_v0001_20260907</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51021_Clin_disorder_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51021_Clin_disorder_v0001_description_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51015_Endo_Metab_v0001_20260907</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51015_Endo_Metab_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51015_Endo_Metab_v0001_description_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51014_Heart_Circ_v0001_20260907</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51014_Heart_Circ_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51014_Heart_Circ_v0001_description_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51013_Respiratory_v0001_20260907</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51013_Respiratory_v0001_description_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-51013_Respiratory_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5252_Alcohol_v0001_20260907</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5252_Alcohol_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5252_Alcohol_v0001_description_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5251_Smoking_v0001_20260907</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5251_Smoking_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5251_Smoking_v0001_description_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5211_EPIC_v0001_20260907</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5211_EPIC_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5211_EPIC_v0001_description_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5151_Econ_Circ_v0001_20260907</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5151_Econ_Circ_v0001_description_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5151_Econ_Circ_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5155_Education_v0001_20260907</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5155_Education_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5155_Education_v0001_description_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5154_Emplymnt_Hist_v0001_20260907</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5154_Emplymnt_Hist_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5154_Emplymnt_Hist_v0001_description_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5152_Household_v0001_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5152_Household_v0001_values_20260907.csv</t>
+  </si>
+  <si>
+    <t>NSHD46_CAT-5152_Household_v0001_description_20260907.csv</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1213,7 +1196,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1253,9 +1235,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1293,7 +1275,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1399,7 +1381,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1541,7 +1523,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1549,1348 +1531,1303 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5527E288-64E3-40B9-871A-CF28D789BFEF}">
-  <dimension ref="A2:AA31"/>
+  <dimension ref="A2:Z31"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" customWidth="1"/>
-    <col min="3" max="4" width="30.42578125" customWidth="1"/>
-    <col min="5" max="5" width="43.7109375" customWidth="1"/>
-    <col min="6" max="6" width="30.42578125" customWidth="1"/>
-    <col min="7" max="8" width="22.85546875" customWidth="1"/>
-    <col min="9" max="9" width="23.28515625" customWidth="1"/>
-    <col min="10" max="10" width="25.140625" customWidth="1"/>
-    <col min="11" max="12" width="26.85546875" customWidth="1"/>
-    <col min="13" max="14" width="22.28515625" customWidth="1"/>
-    <col min="15" max="15" width="27" customWidth="1"/>
-    <col min="16" max="16" width="44.5703125" customWidth="1"/>
-    <col min="17" max="17" width="24.28515625" customWidth="1"/>
-    <col min="18" max="19" width="40.5703125" customWidth="1"/>
-    <col min="20" max="20" width="33.5703125" customWidth="1"/>
-    <col min="21" max="27" width="30.5703125" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
+    <col min="2" max="3" width="30.42578125" customWidth="1"/>
+    <col min="4" max="4" width="43.7109375" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" customWidth="1"/>
+    <col min="6" max="7" width="22.85546875" customWidth="1"/>
+    <col min="8" max="8" width="23.28515625" customWidth="1"/>
+    <col min="9" max="9" width="25.140625" customWidth="1"/>
+    <col min="10" max="11" width="26.85546875" customWidth="1"/>
+    <col min="12" max="13" width="22.28515625" customWidth="1"/>
+    <col min="14" max="14" width="27" customWidth="1"/>
+    <col min="15" max="15" width="44.5703125" customWidth="1"/>
+    <col min="16" max="16" width="24.28515625" customWidth="1"/>
+    <col min="17" max="18" width="40.5703125" customWidth="1"/>
+    <col min="19" max="19" width="33.5703125" customWidth="1"/>
+    <col min="20" max="26" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:27" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="30" t="s">
+    <row r="2" spans="1:26" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
       <c r="H2" s="31"/>
-      <c r="I2" s="32"/>
     </row>
-    <row r="3" spans="1:27" ht="71.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="33" t="s">
+    <row r="3" spans="1:26" ht="71.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
       <c r="H3" s="34"/>
-      <c r="I3" s="35"/>
     </row>
-    <row r="4" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:27" s="1" customFormat="1" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:26" s="1" customFormat="1" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="B5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="C5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="E5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="F5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="H5" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="I5" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="11" t="s">
         <v>10</v>
       </c>
+      <c r="J5" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="K5" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="N5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="O5" s="12" t="s">
         <v>16</v>
       </c>
+      <c r="P5" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="Q5" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y5" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA5" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="1" customFormat="1" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" s="1" customFormat="1" ht="106.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="C6" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="D6" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="E6" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>33</v>
       </c>
+      <c r="G6" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="H6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="N6" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="P6" s="9" t="s">
+      <c r="O6" s="9" t="s">
         <v>41</v>
       </c>
+      <c r="P6" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="Q6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y6" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA6" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:27" s="21" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="B7" s="23">
+    <row r="7" spans="1:26" s="21" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+      <c r="A7" s="23">
         <v>45713</v>
       </c>
+      <c r="B7" s="20" t="s">
+        <v>145</v>
+      </c>
       <c r="C7" s="20" t="s">
-        <v>178</v>
+        <v>55</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="J7" s="20" t="s">
         <v>67</v>
       </c>
+      <c r="J7" s="22" t="s">
+        <v>57</v>
+      </c>
       <c r="K7" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="L7" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="20">
+      <c r="L7" s="20">
         <f>5362-2363</f>
         <v>2999</v>
       </c>
-      <c r="N7" s="20">
+      <c r="M7" s="20">
         <f>5362-2363-313</f>
         <v>2686</v>
       </c>
-      <c r="O7" s="19" t="s">
+      <c r="N7" s="19" t="s">
         <v>64</v>
       </c>
+      <c r="O7" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="P7" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q7" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="R7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S7" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T7" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="U7" s="20" t="s">
         <v>62</v>
       </c>
+      <c r="U7" s="20"/>
       <c r="V7" s="20"/>
-      <c r="W7" s="20"/>
-      <c r="X7" s="20" t="s">
+      <c r="W7" s="20" t="s">
         <v>54</v>
       </c>
+      <c r="X7" s="20"/>
       <c r="Y7" s="20"/>
       <c r="Z7" s="20"/>
-      <c r="AA7" s="20"/>
     </row>
-    <row r="8" spans="1:27" ht="105" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="24">
-        <v>46254</v>
+    <row r="8" spans="1:26" ht="105" x14ac:dyDescent="0.25">
+      <c r="A8" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="K8" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="L8" s="25" t="s">
-        <v>77</v>
+      <c r="L8" s="2">
+        <v>5362</v>
       </c>
       <c r="M8" s="2">
         <v>5362</v>
       </c>
-      <c r="N8" s="2">
-        <v>5362</v>
+      <c r="N8" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="R8" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S8" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T8" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="U8" s="2"/>
       <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X8" s="2"/>
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
-      <c r="AA8" s="2"/>
     </row>
-    <row r="9" spans="1:27" ht="120" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="24">
-        <v>46254</v>
+    <row r="9" spans="1:26" ht="120" x14ac:dyDescent="0.25">
+      <c r="A9" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>109</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>132</v>
+        <v>109</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>53</v>
+        <v>151</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>81</v>
+        <v>150</v>
+      </c>
+      <c r="J9" s="25" t="s">
+        <v>78</v>
       </c>
       <c r="K9" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="L9" s="25" t="s">
-        <v>77</v>
+        <v>75</v>
+      </c>
+      <c r="L9" s="2">
+        <v>5362</v>
       </c>
       <c r="M9" s="2">
         <v>5362</v>
       </c>
-      <c r="N9" s="2">
-        <v>5362</v>
+      <c r="N9" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="R9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S9" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T9" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="U9" s="2"/>
       <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2" t="s">
+      <c r="W9" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X9" s="2"/>
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
-      <c r="AA9" s="2"/>
     </row>
-    <row r="10" spans="1:27" ht="165" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="24">
-        <v>46254</v>
+    <row r="10" spans="1:26" ht="165" x14ac:dyDescent="0.25">
+      <c r="A10" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>110</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>140</v>
+        <v>117</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>86</v>
+        <v>154</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>81</v>
       </c>
       <c r="K10" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="L10" s="25" t="s">
-        <v>77</v>
+        <v>75</v>
+      </c>
+      <c r="L10" s="2">
+        <v>5362</v>
       </c>
       <c r="M10" s="2">
         <v>5362</v>
       </c>
-      <c r="N10" s="2">
-        <v>5362</v>
+      <c r="N10" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="R10" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S10" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T10" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U10" s="2" t="s">
+      <c r="T10" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="U10" s="2"/>
       <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2" t="s">
+      <c r="W10" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X10" s="2"/>
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
-      <c r="AA10" s="2"/>
     </row>
-    <row r="11" spans="1:27" ht="135" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="24">
-        <v>46254</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>95</v>
+    <row r="11" spans="1:26" ht="135" x14ac:dyDescent="0.25">
+      <c r="A11" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>111</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>134</v>
+        <v>111</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>53</v>
+        <v>156</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>92</v>
+        <v>157</v>
+      </c>
+      <c r="J11" s="27" t="s">
+        <v>81</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="L11" s="27" t="s">
-        <v>97</v>
+        <v>87</v>
+      </c>
+      <c r="L11" s="2">
+        <v>5362</v>
       </c>
       <c r="M11" s="2">
         <v>5362</v>
       </c>
-      <c r="N11" s="2">
-        <v>5362</v>
-      </c>
-      <c r="O11" s="26" t="s">
+      <c r="N11" s="26" t="s">
         <v>69</v>
       </c>
+      <c r="O11" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="P11" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="R11" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S11" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T11" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U11" s="2" t="s">
+      <c r="T11" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="U11" s="2"/>
       <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2" t="s">
+      <c r="W11" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X11" s="2"/>
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
     </row>
-    <row r="12" spans="1:27" ht="195" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+    <row r="12" spans="1:26" ht="195" x14ac:dyDescent="0.25">
+      <c r="A12" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="J12" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="K12" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="24">
-        <v>46254</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="K12" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="L12" s="27" t="s">
-        <v>103</v>
+      <c r="L12" s="2">
+        <v>5362</v>
       </c>
       <c r="M12" s="2">
         <v>5362</v>
       </c>
-      <c r="N12" s="2">
-        <v>5362</v>
-      </c>
-      <c r="O12" s="26" t="s">
+      <c r="N12" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="P12" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q12" s="2" t="s">
+      <c r="O12" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="R12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S12" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T12" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="T12" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="U12" s="2"/>
       <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2" t="s">
+      <c r="W12" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X12" s="2"/>
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
-      <c r="AA12" s="2"/>
     </row>
-    <row r="13" spans="1:27" ht="180" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="24">
-        <v>46254</v>
+    <row r="13" spans="1:26" ht="180" x14ac:dyDescent="0.25">
+      <c r="A13" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>107</v>
+        <v>93</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>113</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>141</v>
+        <v>118</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>105</v>
+        <v>163</v>
+      </c>
+      <c r="J13" s="27" t="s">
+        <v>81</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="L13" s="27" t="s">
-        <v>108</v>
+        <v>94</v>
+      </c>
+      <c r="L13" s="2">
+        <v>5362</v>
       </c>
       <c r="M13" s="2">
         <v>5362</v>
       </c>
-      <c r="N13" s="2">
-        <v>5362</v>
-      </c>
-      <c r="O13" s="26" t="s">
+      <c r="N13" s="26" t="s">
         <v>69</v>
       </c>
+      <c r="O13" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="P13" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="R13" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S13" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T13" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U13" s="2" t="s">
+      <c r="T13" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="U13" s="2"/>
       <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2" t="s">
+      <c r="W13" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
-      <c r="AA13" s="2"/>
     </row>
-    <row r="14" spans="1:27" ht="165" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="24">
-        <v>46254</v>
+    <row r="14" spans="1:26" ht="165" x14ac:dyDescent="0.25">
+      <c r="A14" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>112</v>
+        <v>98</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>114</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>142</v>
+        <v>119</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>113</v>
+        <v>166</v>
+      </c>
+      <c r="J14" s="27" t="s">
+        <v>81</v>
       </c>
       <c r="K14" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="L14" s="27" t="s">
-        <v>108</v>
+        <v>94</v>
+      </c>
+      <c r="L14" s="2">
+        <v>5362</v>
       </c>
       <c r="M14" s="2">
         <v>5362</v>
       </c>
-      <c r="N14" s="2">
-        <v>5362</v>
-      </c>
-      <c r="O14" s="26" t="s">
+      <c r="N14" s="26" t="s">
         <v>69</v>
       </c>
+      <c r="O14" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="P14" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="R14" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S14" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T14" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U14" s="2" t="s">
+      <c r="T14" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="U14" s="2"/>
       <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2" t="s">
+      <c r="W14" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
-      <c r="AA14" s="2"/>
     </row>
-    <row r="15" spans="1:27" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="24">
-        <v>46254</v>
+    <row r="15" spans="1:26" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>119</v>
+        <v>100</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>115</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>143</v>
+        <v>120</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>53</v>
+        <v>169</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>117</v>
+        <v>168</v>
+      </c>
+      <c r="J15" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="L15" s="27" t="s">
-        <v>108</v>
+        <v>94</v>
+      </c>
+      <c r="L15" s="2">
+        <v>5362</v>
       </c>
       <c r="M15" s="2">
         <v>5362</v>
       </c>
-      <c r="N15" s="2">
-        <v>5362</v>
-      </c>
-      <c r="O15" s="26" t="s">
+      <c r="N15" s="26" t="s">
         <v>69</v>
       </c>
+      <c r="O15" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="P15" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="R15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S15" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T15" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U15" s="2" t="s">
+      <c r="T15" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="U15" s="2"/>
       <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2" t="s">
+      <c r="W15" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X15" s="2"/>
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
-      <c r="AA15" s="2"/>
     </row>
-    <row r="16" spans="1:27" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:26" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B16" s="24">
-        <v>46254</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="E16" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>144</v>
+        <v>121</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>122</v>
+        <v>172</v>
+      </c>
+      <c r="J16" s="27" t="s">
+        <v>81</v>
       </c>
       <c r="K16" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="L16" s="27" t="s">
-        <v>125</v>
+        <v>104</v>
+      </c>
+      <c r="L16" s="2">
+        <v>5362</v>
       </c>
       <c r="M16" s="2">
         <v>5362</v>
       </c>
-      <c r="N16" s="2">
-        <v>5362</v>
-      </c>
-      <c r="O16" s="26" t="s">
+      <c r="N16" s="26" t="s">
         <v>69</v>
       </c>
+      <c r="O16" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="P16" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q16" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="R16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S16" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T16" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U16" s="2" t="s">
-        <v>111</v>
-      </c>
+      <c r="T16" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="U16" s="2"/>
       <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2" t="s">
+      <c r="W16" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
-      <c r="AA16" s="2"/>
     </row>
-    <row r="17" spans="1:27" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="24">
-        <v>46254</v>
+    <row r="17" spans="1:26" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>129</v>
+        <v>106</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>124</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>150</v>
+        <v>125</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>53</v>
+        <v>174</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>127</v>
+        <v>175</v>
+      </c>
+      <c r="J17" s="27" t="s">
+        <v>107</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="L17" s="27" t="s">
-        <v>125</v>
+        <v>104</v>
+      </c>
+      <c r="L17" s="2">
+        <v>5362</v>
       </c>
       <c r="M17" s="2">
         <v>5362</v>
       </c>
-      <c r="N17" s="2">
-        <v>5362</v>
-      </c>
-      <c r="O17" s="26" t="s">
+      <c r="N17" s="26" t="s">
         <v>69</v>
       </c>
+      <c r="O17" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="P17" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q17" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="R17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S17" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T17" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U17" s="2" t="s">
+      <c r="T17" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="U17" s="2"/>
       <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2" t="s">
+      <c r="W17" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
-      <c r="AA17" s="2"/>
     </row>
-    <row r="18" spans="1:27" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:26" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="J18" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="K18" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="24">
-        <v>46254</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="K18" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="L18" s="27" t="s">
-        <v>103</v>
+      <c r="L18" s="2">
+        <v>5362</v>
       </c>
       <c r="M18" s="2">
         <v>5362</v>
       </c>
-      <c r="N18" s="2">
-        <v>5362</v>
-      </c>
-      <c r="O18" s="26" t="s">
+      <c r="N18" s="26" t="s">
         <v>69</v>
       </c>
+      <c r="O18" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="P18" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="R18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S18" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T18" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U18" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="U18" s="2"/>
       <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2" t="s">
+      <c r="W18" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
-      <c r="AA18" s="2"/>
     </row>
-    <row r="19" spans="1:27" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" s="24">
-        <v>46254</v>
+    <row r="19" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>154</v>
+        <v>127</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>132</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>156</v>
+        <v>129</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>53</v>
+        <v>181</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>152</v>
+        <v>180</v>
+      </c>
+      <c r="J19" s="27" t="s">
+        <v>130</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="L19" s="27" t="s">
-        <v>108</v>
+        <v>94</v>
+      </c>
+      <c r="L19" s="2">
+        <v>5362</v>
       </c>
       <c r="M19" s="2">
         <v>5362</v>
       </c>
-      <c r="N19" s="2">
-        <v>5362</v>
-      </c>
-      <c r="O19" s="26" t="s">
+      <c r="N19" s="26" t="s">
         <v>69</v>
       </c>
+      <c r="O19" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="P19" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q19" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="R19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S19" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T19" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U19" s="2" t="s">
+      <c r="T19" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="U19" s="2"/>
       <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2" t="s">
+      <c r="W19" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
-      <c r="AA19" s="2"/>
     </row>
-    <row r="20" spans="1:27" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="1:26" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="J20" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K20" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="24">
-        <v>46254</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K20" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="L20" s="27" t="s">
-        <v>103</v>
+      <c r="L20" s="2">
+        <v>5362</v>
       </c>
       <c r="M20" s="2">
         <v>5362</v>
       </c>
-      <c r="N20" s="2">
-        <v>5362</v>
-      </c>
-      <c r="O20" s="26" t="s">
+      <c r="N20" s="26" t="s">
         <v>69</v>
       </c>
+      <c r="O20" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="P20" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q20" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="R20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S20" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T20" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U20" s="2" t="s">
+      <c r="T20" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="U20" s="2"/>
       <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2" t="s">
+      <c r="W20" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X20" s="2"/>
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
-      <c r="AA20" s="2"/>
     </row>
-    <row r="21" spans="1:27" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="24">
-        <v>46254</v>
+    <row r="21" spans="1:26" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>170</v>
+        <v>139</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>137</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>169</v>
+        <v>138</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>53</v>
+        <v>186</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>166</v>
+        <v>187</v>
+      </c>
+      <c r="J21" s="27" t="s">
+        <v>81</v>
       </c>
       <c r="K21" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="L21" s="27" t="s">
-        <v>108</v>
+        <v>94</v>
+      </c>
+      <c r="L21" s="2">
+        <v>5362</v>
       </c>
       <c r="M21" s="2">
         <v>5362</v>
       </c>
-      <c r="N21" s="2">
-        <v>5362</v>
-      </c>
-      <c r="O21" s="26" t="s">
+      <c r="N21" s="26" t="s">
         <v>69</v>
       </c>
+      <c r="O21" s="2" t="s">
+        <v>140</v>
+      </c>
       <c r="P21" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q21" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="R21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S21" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T21" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U21" s="2" t="s">
+      <c r="T21" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="U21" s="2"/>
       <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2" t="s">
+      <c r="W21" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
-      <c r="AA21" s="2"/>
     </row>
-    <row r="22" spans="1:27" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="24">
-        <v>46254</v>
+    <row r="22" spans="1:26" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="24">
+        <v>46272</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>174</v>
+        <v>141</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>142</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>176</v>
+        <v>143</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>172</v>
+        <v>190</v>
+      </c>
+      <c r="J22" s="27" t="s">
+        <v>78</v>
       </c>
       <c r="K22" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="L22" s="27" t="s">
-        <v>108</v>
+        <v>94</v>
+      </c>
+      <c r="L22" s="2">
+        <v>5362</v>
       </c>
       <c r="M22" s="2">
         <v>5362</v>
       </c>
-      <c r="N22" s="2">
-        <v>5362</v>
-      </c>
-      <c r="O22" s="26" t="s">
+      <c r="N22" s="26" t="s">
         <v>69</v>
       </c>
+      <c r="O22" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="P22" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q22" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="R22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="S22" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="T22" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="U22" s="2" t="s">
+      <c r="T22" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="U22" s="2"/>
       <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2" t="s">
+      <c r="W22" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
-      <c r="AA22" s="2"/>
     </row>
-    <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -2916,9 +2853,9 @@
       <c r="X23" s="2"/>
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
-      <c r="AA23" s="2"/>
     </row>
-    <row r="24" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -2944,9 +2881,9 @@
       <c r="X24" s="2"/>
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
-      <c r="AA24" s="2"/>
     </row>
-    <row r="25" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -2972,9 +2909,9 @@
       <c r="X25" s="2"/>
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
-      <c r="AA25" s="2"/>
     </row>
-    <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -3000,9 +2937,9 @@
       <c r="X26" s="2"/>
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
-      <c r="AA26" s="2"/>
     </row>
-    <row r="27" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -3028,9 +2965,9 @@
       <c r="X27" s="2"/>
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
-      <c r="AA27" s="2"/>
     </row>
-    <row r="28" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -3056,9 +2993,9 @@
       <c r="X28" s="2"/>
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
-      <c r="AA28" s="2"/>
     </row>
-    <row r="29" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -3084,9 +3021,9 @@
       <c r="X29" s="2"/>
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
-      <c r="AA29" s="2"/>
     </row>
-    <row r="30" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -3112,9 +3049,9 @@
       <c r="X30" s="2"/>
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
-      <c r="AA30" s="2"/>
     </row>
-    <row r="31" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -3140,12 +3077,11 @@
       <c r="X31" s="2"/>
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
-      <c r="AA31" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -3153,33 +3089,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="edb9d0e4-5370-4cfb-9e4e-bdf6de379f60" xsi:nil="true"/>
-    <SharedWithUsers xmlns="bc464197-6a6a-4722-a0be-b24c34e3dd9e">
-      <UserInfo>
-        <DisplayName>Samantha Berman</DisplayName>
-        <AccountId>50</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b8c92ccb-f7f9-43b8-b828-8634382970d0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010071FB26ED47B7A040B9694E280C8A028C" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="51694721c5993bd1d7ee31732747c74d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b8c92ccb-f7f9-43b8-b828-8634382970d0" xmlns:ns3="bc464197-6a6a-4722-a0be-b24c34e3dd9e" xmlns:ns4="edb9d0e4-5370-4cfb-9e4e-bdf6de379f60" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2abadf83116fb303de7750466b9c1ce8" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b8c92ccb-f7f9-43b8-b828-8634382970d0"/>
@@ -3433,27 +3342,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B64A78E-FA98-4BD6-A16D-D65CD3857185}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="edb9d0e4-5370-4cfb-9e4e-bdf6de379f60"/>
-    <ds:schemaRef ds:uri="bc464197-6a6a-4722-a0be-b24c34e3dd9e"/>
-    <ds:schemaRef ds:uri="b8c92ccb-f7f9-43b8-b828-8634382970d0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8194028F-5AB4-417F-915C-72EAB37A02CF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="edb9d0e4-5370-4cfb-9e4e-bdf6de379f60" xsi:nil="true"/>
+    <SharedWithUsers xmlns="bc464197-6a6a-4722-a0be-b24c34e3dd9e">
+      <UserInfo>
+        <DisplayName>Samantha Berman</DisplayName>
+        <AccountId>50</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b8c92ccb-f7f9-43b8-b828-8634382970d0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04EE2F2F-2877-498F-B100-D17CB7202974}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3471,4 +3387,24 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8194028F-5AB4-417F-915C-72EAB37A02CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B64A78E-FA98-4BD6-A16D-D65CD3857185}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="edb9d0e4-5370-4cfb-9e4e-bdf6de379f60"/>
+    <ds:schemaRef ds:uri="bc464197-6a6a-4722-a0be-b24c34e3dd9e"/>
+    <ds:schemaRef ds:uri="b8c92ccb-f7f9-43b8-b828-8634382970d0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>